--- a/Formning_standard.xlsx
+++ b/Formning_standard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onedometic-my.sharepoint.com/personal/martin_petersson_dometic_com/Documents/Skrivbordet/HOME1/Apps/Frekvensanalys/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="322" documentId="8_{5B1E7E70-6A2C-4FA5-9913-59E9EA794D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F07A90FB-B584-4FC0-A082-615781546A16}"/>
+  <xr:revisionPtr revIDLastSave="324" documentId="8_{5B1E7E70-6A2C-4FA5-9913-59E9EA794D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12C8C008-6CE7-4DE1-85FA-37B0D73970B8}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44415" yWindow="5625" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="26">
   <si>
     <t>Kategori</t>
   </si>
@@ -47,12 +47,6 @@
     <t>Aktivitet</t>
   </si>
   <si>
-    <t>Övrigt</t>
-  </si>
-  <si>
-    <t>Gång</t>
-  </si>
-  <si>
     <t>Kör maskin</t>
   </si>
   <si>
@@ -120,60 +114,6 @@
   </si>
   <si>
     <t>Rensa bort fel material</t>
-  </si>
-  <si>
-    <t>Omställning</t>
-  </si>
-  <si>
-    <t>Byta verktyg</t>
-  </si>
-  <si>
-    <t>Hämta verktyg</t>
-  </si>
-  <si>
-    <t>Rengöra verktyg</t>
-  </si>
-  <si>
-    <t>Kontrollera första bit</t>
-  </si>
-  <si>
-    <t>Justera efter första bit</t>
-  </si>
-  <si>
-    <t>Dokumentera omställning</t>
-  </si>
-  <si>
-    <t>Störning</t>
-  </si>
-  <si>
-    <t>Vänta på material</t>
-  </si>
-  <si>
-    <t>Vänta på truck</t>
-  </si>
-  <si>
-    <t>Vänta på tekniker</t>
-  </si>
-  <si>
-    <t>Maskinstopp</t>
-  </si>
-  <si>
-    <t>Kvalitetsproblem</t>
-  </si>
-  <si>
-    <t>Saknar information</t>
-  </si>
-  <si>
-    <t>Prata med lagledare</t>
-  </si>
-  <si>
-    <t>Hjälpa annan operatör</t>
-  </si>
-  <si>
-    <t>Vänta</t>
-  </si>
-  <si>
-    <t>Annat arbete</t>
   </si>
 </sst>
 </file>
@@ -400,8 +340,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF48DA23-3E59-4607-B2B4-8A642AED3858}" name="Table1" displayName="Table1" ref="A1:C38" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
-  <autoFilter ref="A1:C38" xr:uid="{BF48DA23-3E59-4607-B2B4-8A642AED3858}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF48DA23-3E59-4607-B2B4-8A642AED3858}" name="Table1" displayName="Table1" ref="A1:C21" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
+  <autoFilter ref="A1:C21" xr:uid="{BF48DA23-3E59-4607-B2B4-8A642AED3858}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{A3768F14-CCAD-44BA-BF45-88778F5F665B}" name="Kategori" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{C4189BEF-9E3C-4B91-9321-6CBA1D620671}" name="Underkategori"/>
@@ -701,7 +641,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -727,417 +667,230 @@
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C43:C1048576 C1">
+  <conditionalFormatting sqref="C26:C1048576 C1">
     <cfRule type="duplicateValues" dxfId="2" priority="294"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C43:C1048576">
+  <conditionalFormatting sqref="C26:C1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="296"/>
     <cfRule type="duplicateValues" dxfId="0" priority="298"/>
   </conditionalFormatting>
